--- a/artfynd/A 63895-2023 artfynd.xlsx
+++ b/artfynd/A 63895-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63895-2023 artfynd.xlsx
+++ b/artfynd/A 63895-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439749</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669841</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95670070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439739</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669739</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439740</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439741</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439742</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439748</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1749,6 +1799,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95670007</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1868,6 +1923,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95670021</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1977,6 +2037,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95670324</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2078,6 +2143,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439736</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,6 +2249,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439737</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2280,6 +2355,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439738</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2381,6 +2461,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439743</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2482,6 +2567,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439744</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2583,6 +2673,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439746</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2684,6 +2779,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439750</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2793,6 +2893,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95670031</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2890,6 +2995,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824954</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2991,6 +3101,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439745</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3088,6 +3203,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824919</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3185,6 +3305,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824921</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3282,6 +3407,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824937</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3379,6 +3509,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824939</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3476,6 +3611,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824943</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3573,6 +3713,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824951</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3670,6 +3815,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824920</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3767,6 +3917,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824929</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3868,6 +4023,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669902</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3969,6 +4129,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439751</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4088,6 +4253,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669802</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4207,6 +4377,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669863</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4326,6 +4501,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669816</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4445,6 +4625,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669829</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4554,6 +4739,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669850</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4663,6 +4853,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669891</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4782,6 +4977,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669936</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4891,6 +5091,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95670041</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4988,6 +5193,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824926</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5085,6 +5295,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824927</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5182,6 +5397,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824933</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5279,6 +5499,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824936</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5376,6 +5601,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824940</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5482,6 +5712,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888608</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5588,6 +5823,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888607</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5689,6 +5929,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669752</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5806,6 +6051,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669670</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5903,6 +6153,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824931</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6000,6 +6255,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824949</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6106,6 +6366,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888606</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6207,8 +6472,68 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>